--- a/data/toyota_raw.xlsx
+++ b/data/toyota_raw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ottob\Documents\Projects\Data Analytics\ghg-emissions-benchmarking\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76E4625-931F-4415-83D7-41942AFECA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A70C769-FA80-42AE-A540-C4BFBF19D390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="138">
   <si>
     <t>Toyota Sustainability Data Book 2025</t>
   </si>
@@ -249,10 +249,6 @@
   </si>
   <si>
     <t>Not verified under limited assurance engagement for the year ended March 31, 2025.</t>
-  </si>
-  <si>
-    <t>Not restated — see Data Book 2024, p.53. 
-Calculated based on 10,000 tons of CO₂ — see Data Book 2025, p.61, fn.7.</t>
   </si>
   <si>
     <t>Recorded under scope 1 and 2 — see Data Book 2025, p.61, fn.3.</t>
@@ -287,10 +283,6 @@
 Not verified under limited assurance engagement for the year ended March 31, 2025.</t>
   </si>
   <si>
-    <t>Not restated — see Data Book 2023, p.48. 
-Calculated based on 10,000 tons of CO₂ — see Data Book 2025, p.61, fn.7.</t>
-  </si>
-  <si>
     <t>Restated — see Data Book 2023, p.48: (0.12 million t-CO₂). 
 Calculation conditions changed based on JAMA guidelines — see Data Book 2025, p.61, fn.4.</t>
   </si>
@@ -303,12 +295,6 @@
 Current value not verified under limited assurance engagement for the year ended March 31, 2025.</t>
   </si>
   <si>
-    <t>Restated — see Data Book 2023, p.48: (570.49 million t-CO₂).</t>
-  </si>
-  <si>
-    <t>Restated — see Data Book 2024, p.53: (587.46 million t-CO₂).</t>
-  </si>
-  <si>
     <t>Not restated — see Data Book 2023, p.47.</t>
   </si>
   <si>
@@ -316,12 +302,6 @@
   </si>
   <si>
     <t>Not republished in Data Book 2025; value taken from the original report.</t>
-  </si>
-  <si>
-    <t>Not restated — see Integrated Report 2024, p.133.</t>
-  </si>
-  <si>
-    <t>Not restated — see Integrated Report 2023, p.103.</t>
   </si>
   <si>
     <t>Original value not verified under limited assurance engagement for the year ended March 31, 2024. 
@@ -497,20 +477,6 @@
         <family val="2"/>
       </rPr>
       <t>https://github.com/johnpatrickgarcia-da/ghg-emissions-benchmarking</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">WORKBOOK: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>v1.0, 2026-10-16</t>
     </r>
   </si>
   <si>
@@ -568,7 +534,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">◦ Revenue and JPY to USD exchange rate (FY2023–FY2025); </t>
+    <t>◦ Revenue and JPY to USD exchange rate (FY2023–FY2025)</t>
   </si>
   <si>
     <t>◦ Original FY2024 revenue and exchange rate, for restatement checks</t>
@@ -730,9 +696,9 @@
 ◦ Original FY2023 emissions and headcount values and assurance, for restatement and assurance checks</t>
   </si>
   <si>
-    <t xml:space="preserve">◦ Scope 1, Scope 2 (market-based) and Scope 3 (total and all 15 categories), FY2023–FY2025, with assurance status and gas-basis notes; 
+    <t>◦ Scope 1, Scope 2 (market-based) and Scope 3 (total and all 15 categories), FY2023–FY2025, with assurance status and gas-basis notes; 
 ◦ Headcount (FY2023–FY2025); 
-◦ Units sold (FY2025); </t>
+◦ Units sold (FY2025)</t>
   </si>
   <si>
     <r>
@@ -763,12 +729,51 @@
     </r>
   </si>
   <si>
-    <t>Restated — see Data Book 2024, p.53: (123.80 million t-CO₂). 
-Methodology changed based on the Japan Automobile Manufacturers Association (JAMA) guidelines — see Data Book 2025, p.61, fn.1.</t>
-  </si>
-  <si>
     <t>Restated — see Data Book 2023, p.48: (110.49 million t-CO₂). 
 Methodology changed based on the Japan Automobile Manufacturers Association (JAMA) guidelines — see Data Book 2025, p.61, fn.1.</t>
+  </si>
+  <si>
+    <t>Not restated — see Data Book 2024, p.53. 
+Reported on a CO₂-only basis for this year (Toyota: “Calculated based on CO2 (10,000 tons of CO₂) for the years 2022 and 2023”) — see Data Book 2025, p.61, fn.7.</t>
+  </si>
+  <si>
+    <t>Not restated — see Data Book 2023, p.48. 
+Reported on a CO₂-only basis for this year (Toyota: “Calculated based on CO2 (10,000 tons of CO₂) for the years 2022 and 2023”) — see Data Book 2025, p.61, fn.7.</t>
+  </si>
+  <si>
+    <t>Some emissions recorded are under category 11 in scope 3 — see Data Book 2025, p.61, fn.2.</t>
+  </si>
+  <si>
+    <t>Restated — see Data Book 2024, p.53: (123.80 million t-CO₂e). 
+Methodology changed based on the Japan Automobile Manufacturers Association (JAMA) guidelines — see Data Book 2025, p.61, fn.1.</t>
+  </si>
+  <si>
+    <t>Not restated — see Integrated Report 2024, p.133.</t>
+  </si>
+  <si>
+    <t>Not restated — see Integrated Report 2023, p.103.</t>
+  </si>
+  <si>
+    <t>Restated — see Data Book 2024, p.53: (587.46 million t-CO₂). 
+Includes Categories 3, 4, 6, 7, 9, 13 and 14 on a CO₂-only basis (Data Book 2025, p.61, fn.7), so the total mixes CO₂ and CO₂e.</t>
+  </si>
+  <si>
+    <t>Restated — see Data Book 2023, p.48: (570.49 million t-CO₂). 
+Includes Categories 3, 4, 6, 7, 9 and 14 on a CO₂-only basis (Data Book 2025, p.61, fn.7), so the total mixes CO₂ and CO₂e.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WORKBOOK: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>v1.0, 2026-10-17</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1432,7 +1437,7 @@
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="8"/>
       <c r="B1" s="21" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
@@ -1441,7 +1446,7 @@
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8"/>
       <c r="B2" s="20" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -1450,7 +1455,7 @@
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="B3" s="20" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1459,7 +1464,7 @@
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8"/>
       <c r="B4" s="19" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
@@ -1482,7 +1487,7 @@
     <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="12" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -1491,7 +1496,7 @@
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="23" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -1500,7 +1505,7 @@
     <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="23" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
@@ -1509,7 +1514,7 @@
     <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="23" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
@@ -1518,7 +1523,7 @@
     <row r="11" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="23" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -1541,7 +1546,7 @@
     <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="15" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -1550,13 +1555,13 @@
     <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="14" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E15" s="13"/>
     </row>
@@ -1566,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E16" s="13"/>
     </row>
@@ -1579,10 +1584,10 @@
         <v>57</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E17" s="13"/>
     </row>
@@ -1592,10 +1597,10 @@
         <v>58</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E18" s="13"/>
     </row>
@@ -1605,36 +1610,36 @@
         <v>51</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
       <c r="B20" s="17" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>
       <c r="B21" s="17" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E21" s="13"/>
     </row>
@@ -1655,7 +1660,7 @@
     <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>
       <c r="B24" s="15" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -1664,7 +1669,7 @@
     <row r="25" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>
       <c r="B25" s="24" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -1673,10 +1678,10 @@
     <row r="26" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>
       <c r="B26" s="16" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="13"/>
@@ -1684,7 +1689,7 @@
     <row r="27" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>
       <c r="B27" s="22" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C27" s="22"/>
       <c r="D27" s="22"/>
@@ -1825,7 +1830,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>42</v>
@@ -1891,7 +1896,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>8</v>
@@ -1923,7 +1928,7 @@
         <v>125</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -1953,7 +1958,7 @@
         <v>125</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -1983,7 +1988,7 @@
         <v>125</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -2041,7 +2046,7 @@
         <v>163</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -2071,7 +2076,7 @@
         <v>163</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -2129,7 +2134,7 @@
         <v>163</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -2159,7 +2164,7 @@
         <v>163</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -2171,7 +2176,7 @@
         <v>45747</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D11" s="6">
         <v>9362410</v>
@@ -2199,7 +2204,7 @@
         <v>45382</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D12" s="6">
         <v>9442770</v>
@@ -2217,7 +2222,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J12" s="3"/>
     </row>
@@ -2229,7 +2234,7 @@
         <v>45016</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D13" s="6">
         <v>8821872</v>
@@ -2247,7 +2252,7 @@
         <v>5</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J13" s="3"/>
     </row>
@@ -2297,7 +2302,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>6</v>
@@ -2306,10 +2311,10 @@
         <v>7</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>8</v>
@@ -2384,10 +2389,10 @@
         <v>60</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M3" s="3"/>
     </row>
@@ -2423,10 +2428,10 @@
         <v>60</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M4" s="3"/>
     </row>
@@ -2462,7 +2467,7 @@
         <v>28</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -2499,7 +2504,7 @@
         <v>28</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -2536,7 +2541,7 @@
         <v>28</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -2573,7 +2578,7 @@
         <v>60</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>67</v>
@@ -2612,10 +2617,10 @@
         <v>60</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M9" s="3"/>
     </row>
@@ -2651,10 +2656,10 @@
         <v>60</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M10" s="3"/>
     </row>
@@ -2727,10 +2732,10 @@
         <v>61</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M12" s="3"/>
     </row>
@@ -2766,10 +2771,10 @@
         <v>61</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M13" s="3"/>
     </row>
@@ -2853,7 +2858,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>6</v>
@@ -2862,10 +2867,10 @@
         <v>7</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -2946,10 +2951,10 @@
         <v>61</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -2988,10 +2993,10 @@
         <v>61</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -3070,10 +3075,10 @@
         <v>61</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -3112,10 +3117,10 @@
         <v>61</v>
       </c>
       <c r="L7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="N7" s="3"/>
     </row>
@@ -3194,10 +3199,10 @@
         <v>61</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N9" s="3"/>
     </row>
@@ -3236,10 +3241,10 @@
         <v>61</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N10" s="3"/>
     </row>
@@ -3318,10 +3323,10 @@
         <v>61</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N12" s="3"/>
     </row>
@@ -3360,10 +3365,10 @@
         <v>61</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N13" s="3"/>
     </row>
@@ -3442,10 +3447,10 @@
         <v>61</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N15" s="3"/>
     </row>
@@ -3484,10 +3489,10 @@
         <v>61</v>
       </c>
       <c r="L16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="N16" s="3"/>
     </row>
@@ -3525,7 +3530,9 @@
       <c r="K17" s="3">
         <v>61</v>
       </c>
-      <c r="L17" s="3"/>
+      <c r="L17" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="M17" s="3" t="s">
         <v>68</v>
       </c>
@@ -3566,10 +3573,10 @@
         <v>61</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N18" s="3"/>
     </row>
@@ -3608,10 +3615,10 @@
         <v>61</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N19" s="3"/>
     </row>
@@ -3650,7 +3657,7 @@
         <v>61</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>68</v>
@@ -3692,10 +3699,10 @@
         <v>61</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N21" s="3"/>
     </row>
@@ -3734,10 +3741,10 @@
         <v>61</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N22" s="3"/>
     </row>
@@ -3776,7 +3783,7 @@
         <v>28</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -3816,7 +3823,7 @@
         <v>28</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
@@ -3856,7 +3863,7 @@
         <v>28</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3936,10 +3943,10 @@
         <v>61</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N27" s="3"/>
     </row>
@@ -3978,10 +3985,10 @@
         <v>61</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N28" s="3"/>
     </row>
@@ -4060,10 +4067,10 @@
         <v>61</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N30" s="3"/>
     </row>
@@ -4102,10 +4109,10 @@
         <v>61</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N31" s="3"/>
     </row>
@@ -4184,10 +4191,10 @@
         <v>61</v>
       </c>
       <c r="L33" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M33" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="N33" s="3"/>
     </row>
@@ -4226,10 +4233,10 @@
         <v>61</v>
       </c>
       <c r="L34" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M34" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="N34" s="3"/>
     </row>
@@ -4308,10 +4315,10 @@
         <v>61</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N36" s="3"/>
     </row>
@@ -4350,10 +4357,10 @@
         <v>61</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N37" s="3"/>
     </row>
@@ -4391,7 +4398,9 @@
       <c r="K38" s="3">
         <v>61</v>
       </c>
-      <c r="L38" s="3"/>
+      <c r="L38" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="M38" s="3" t="s">
         <v>68</v>
       </c>
@@ -4432,10 +4441,10 @@
         <v>61</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N39" s="3"/>
     </row>
@@ -4474,7 +4483,7 @@
         <v>28</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4513,7 +4522,9 @@
       <c r="K41" s="3">
         <v>61</v>
       </c>
-      <c r="L41" s="3"/>
+      <c r="L41" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="M41" s="3" t="s">
         <v>68</v>
       </c>
@@ -4554,10 +4565,10 @@
         <v>61</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N42" s="3"/>
     </row>
@@ -4596,10 +4607,10 @@
         <v>61</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N43" s="3"/>
     </row>
@@ -4678,10 +4689,10 @@
         <v>61</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N45" s="3"/>
     </row>
@@ -4720,10 +4731,10 @@
         <v>61</v>
       </c>
       <c r="L46" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M46" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="N46" s="3"/>
     </row>
@@ -4797,7 +4808,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
